--- a/artfynd/A 17705-2023 artfynd.xlsx
+++ b/artfynd/A 17705-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17705-2023 artfynd.xlsx
+++ b/artfynd/A 17705-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55936050</v>
+        <v>55936049</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758092.0429373132</v>
+        <v>758092</v>
       </c>
       <c r="R2" t="n">
-        <v>7527673.141933876</v>
+        <v>7527673</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,27 +743,18 @@
           <t>2014-09-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55936049</v>
+        <v>110050080</v>
       </c>
       <c r="B3" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +784,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ongelmus, T lm</t>
+          <t>Ongelmus-Vathaanvaara, T lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758092.0429373132</v>
+        <v>758112</v>
       </c>
       <c r="R3" t="n">
-        <v>7527673.141933876</v>
+        <v>7527378</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +838,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-09-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-09-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,56 +852,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sture Westerberg, Robert Sandberg, Frédéric Forsmark</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110050076</v>
+        <v>110050070</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +905,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758102.7816354672</v>
+        <v>758102</v>
       </c>
       <c r="R4" t="n">
-        <v>7527510.960985144</v>
+        <v>7527534</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,19 +938,9 @@
           <t>2022-09-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,37 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110050071</v>
+        <v>110050079</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758003.0610125849</v>
+        <v>758110</v>
       </c>
       <c r="R5" t="n">
-        <v>7527557.905490503</v>
+        <v>7527383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,19 +1035,9 @@
           <t>2022-09-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,15 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110050070</v>
+        <v>110050081</v>
       </c>
       <c r="B6" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,21 +1075,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1164,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>758102.3870998403</v>
+        <v>758081</v>
       </c>
       <c r="R6" t="n">
-        <v>7527534.188832497</v>
+        <v>7527344</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,19 +1132,9 @@
           <t>2022-09-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,6 +1158,796 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>55936050</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ongelmus, T lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>758092</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7527673</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2014-09-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2014-09-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sture Westerberg, Robert Sandberg, Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>110050071</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ongelmus-Vathaanvaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>758003</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7527558</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>110050073</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ongelmus-Vathaanvaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>758110</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7527399</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>110050076</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ongelmus-Vathaanvaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>758103</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7527511</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110050072</v>
+      </c>
+      <c r="B11" t="n">
+        <v>89156</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ongelmus-Vathaanvaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>758184</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7527473</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>103501337</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kiruna, T lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>758102</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7527385</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110050067</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ongelmus-Vathaanvaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>758256</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7527759</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>110050075</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ongelmus-Vathaanvaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>758088</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7527529</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17705-2023 artfynd.xlsx
+++ b/artfynd/A 17705-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1854,48 +1854,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110050075</v>
+        <v>134500464</v>
       </c>
       <c r="B14" t="n">
-        <v>58057</v>
+        <v>58461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>103018</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ongelmus-Vathaanvaara, T lm</t>
+          <t>Paurankinsivu, Paurankinsivu, T lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>758088</v>
+        <v>757649</v>
       </c>
       <c r="R14" t="n">
-        <v>7527529</v>
+        <v>7527194</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1919,12 +1919,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-11</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1939,15 +1949,112 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>110050075</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ongelmus-Vathaanvaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>758088</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7527529</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-09-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Robert Sandberg</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>per-erik mukka</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17705-2023 artfynd.xlsx
+++ b/artfynd/A 17705-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55936049</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050080</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050070</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050079</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050081</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55936050</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050071</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050073</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050076</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050072</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1754,6 +1809,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103501337</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1851,6 +1911,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050067</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1958,6 +2023,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134500464</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2055,8 +2125,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110050075</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>